--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2451,7 +2451,11 @@
           <t>CARMEL INFRA</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2478,7 +2482,11 @@
           <t>CARMEL INFRA</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -2820,7 +2828,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2828,11 +2836,7 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2847,7 +2851,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
@@ -2855,7 +2859,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2863,7 +2867,11 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2886,7 +2894,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2909,20 +2917,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -2948,7 +2956,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2979,7 +2987,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3010,7 +3018,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3018,11 +3026,7 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3037,7 +3041,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
@@ -3045,7 +3049,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3053,7 +3057,11 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3063,25 +3071,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3107,7 +3115,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3138,10 +3146,14 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+          <t>BORDEAUX INFRA</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
@@ -3165,7 +3177,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3196,7 +3208,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3219,20 +3231,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -3258,7 +3270,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3289,7 +3301,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3307,25 +3319,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>47343</v>
+        <v>46199</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -3333,37 +3345,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>46454</v>
+        <v>47343</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3386,7 +3394,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3396,7 +3404,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3429,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3443,30 +3451,30 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>46083</v>
+        <v>46454</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3499,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3501,7 +3509,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3513,16 +3521,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>47217</v>
+        <v>46083</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3531,12 +3539,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3561,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
@@ -3566,12 +3574,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBMGBLFI7Q4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>609712-LFS</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3596,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LFSC19002HS</t>
+          <t>LFSC19002CE</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
@@ -3601,10 +3609,45 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LFSC19002HS</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>

--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1846,27 +1846,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>45582</v>
+        <v>47217</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>BRABCBLFN7I2</t>
-        </is>
-      </c>
+          <t>JERA2026 FIM</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1877,27 +1873,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
+          <t>LFSC19002CE</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>45582</v>
+        <v>47217</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>BRABCBLFN7I2</t>
-        </is>
-      </c>
+          <t>JERA2026 FIM</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1908,27 +1900,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
+          <t>LFSC19002HS</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>45582</v>
+        <v>47217</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>BRABCBLFN7I2</t>
-        </is>
-      </c>
+          <t>JERA2026 FIM</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1939,25 +1927,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>45454</v>
+        <v>45582</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BRBNBRLFI013</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -1970,25 +1958,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>45454</v>
+        <v>45582</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2001,25 +1989,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45454</v>
+        <v>45582</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2037,7 +2025,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -2050,7 +2038,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2076,7 +2064,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2099,20 +2087,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>45455</v>
+        <v>45454</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2130,11 +2118,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>45455</v>
+        <v>45454</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2143,7 +2131,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -2161,20 +2149,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45455</v>
+        <v>45454</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -2192,11 +2180,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>45461</v>
+        <v>45455</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2205,7 +2193,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -2223,11 +2211,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>45461</v>
+        <v>45455</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2236,7 +2224,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -2254,11 +2242,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>45462</v>
+        <v>45455</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2267,7 +2255,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2285,20 +2273,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>45464</v>
+        <v>45461</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -2316,20 +2304,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>45464</v>
+        <v>45461</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2342,25 +2330,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>45582</v>
+        <v>45462</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI0F8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -2368,21 +2356,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>46181</v>
+        <v>45464</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2391,7 +2379,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -2399,30 +2387,30 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>46240</v>
+        <v>45464</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -2430,30 +2418,30 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19007G2</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>46181</v>
+        <v>45582</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRABCBLFIM30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -2475,11 +2463,11 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2497,25 +2485,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2528,32 +2516,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>46237</v>
+        <v>46181</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2563,25 +2547,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2594,25 +2578,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTR2X9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2625,28 +2609,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2656,32 +2644,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+          <t>BRBBDCLTROH4</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2691,25 +2675,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>45929</v>
+        <v>46251</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
+          <t>BRBSAFLNN8B3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -2727,20 +2711,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>46332</v>
+        <v>46251</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRBSAFLNN8B3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -2758,23 +2742,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>46395</v>
+        <v>46251</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2784,25 +2772,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>46486</v>
+        <v>45929</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -2815,25 +2803,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>46486</v>
+        <v>46332</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -2846,32 +2834,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>46486</v>
+        <v>46395</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNBB5</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2886,7 +2870,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
@@ -2894,7 +2878,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2917,7 +2901,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
@@ -2925,7 +2909,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2948,23 +2932,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>BRBPACLFIVQ4</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2979,20 +2967,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -3010,20 +2998,20 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -3049,7 +3037,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3057,11 +3045,7 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3076,7 +3060,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
@@ -3084,7 +3068,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3102,25 +3086,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -3133,28 +3117,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>BRBPACLFIWC2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3164,25 +3152,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -3208,7 +3196,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3239,7 +3227,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3262,20 +3250,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -3293,20 +3281,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -3324,11 +3312,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3337,7 +3325,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -3350,25 +3338,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>47343</v>
+        <v>46199</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -3376,107 +3364,95 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>46454</v>
+        <v>46199</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>46454</v>
+        <v>46199</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>46454</v>
+        <v>47343</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3486,16 +3462,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>46083</v>
+        <v>46454</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3504,7 +3480,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3521,16 +3497,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>46083</v>
+        <v>46454</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3539,7 +3515,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3556,30 +3532,30 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>47217</v>
+        <v>46454</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3591,30 +3567,30 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>47217</v>
+        <v>46083</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3626,28 +3602,133 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>BANCO XP</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LF00240072E</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>BRBCXPLFIKS5</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>BANCO BMG S.A.</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>LFSC19002CD</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>609712-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
         <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
+      <c r="D104" s="2" t="n">
         <v>47217</v>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>JERA2026</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>

--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,25 +1175,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>BANCO RANDON</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CDB925CDN0L</t>
+          <t>CDB8265ICFV</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>46013</v>
+        <v>46359</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BRBVKWC01543</t>
+          <t>BRRANDC001H9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1201,21 +1201,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
+          <t>BANCO RANDON</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HAPV21</t>
+          <t>CDB8265ICFW</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>46213</v>
+        <v>46359</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BRHAPVDBS014</t>
+          <t>BRRANDC001H9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1232,65 +1232,61 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
+          <t>BANCO RANDON</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HAPV21</t>
+          <t>CDB8265ICFX</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>46213</v>
+        <v>46359</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BRHAPVDBS014</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>362409-HAP</t>
-        </is>
-      </c>
+          <t>BRRANDC001H9</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>BANCO RANDON</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>CDB8265ICFY</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>47196</v>
+        <v>46359</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
+          <t>BRRANDC001H9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1298,30 +1294,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>BANCO RANDON</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>CDB8265ICFZ</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>47196</v>
+        <v>46359</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
+          <t>BRRANDC001H9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1329,30 +1325,30 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>CDB925CDN0L</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>47196</v>
+        <v>46013</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
+          <t>BRBVKWC01543</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1365,25 +1361,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>HAPV21</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>47196</v>
+        <v>46213</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
+          <t>BRHAPVDBS014</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1396,60 +1392,60 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>HAPV21</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>47196</v>
+        <v>46213</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
+          <t>BRHAPVDBS014</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>353017-KLB</t>
+          <t>362409-HAP</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>46083</v>
+        <v>47196</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRKLBNDBS004</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1457,30 +1453,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LF0024007Y4</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>46097</v>
+        <v>47196</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO68</t>
+          <t>BRKLBNDBS004</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -1488,65 +1484,61 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LF0024008OB</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>46104</v>
+        <v>47196</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO76</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRKLBNDBS004</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LF0024008OB</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>46104</v>
+        <v>47196</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO76</t>
+          <t>BRKLBNDBS004</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1554,33 +1546,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LF002400KBT</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>46234</v>
+        <v>47196</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>BRKLBNDBS004</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>353017-KLB</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1590,25 +1586,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LF002400KBU</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>46234</v>
+        <v>46083</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1621,16 +1617,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LF002400KBW</t>
+          <t>LF0024007Y4</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>46234</v>
+        <v>46097</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1639,7 +1635,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIO68</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -1652,28 +1648,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LF002400KBX</t>
+          <t>LF0024008OB</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>46234</v>
+        <v>46104</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>BRBCXPLFIO76</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1683,25 +1683,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LF002400KBY</t>
+          <t>LF0024008OB</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>46234</v>
+        <v>46104</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIO76</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LF002400KC0</t>
+          <t>LF002400KBT</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LF002400KC0</t>
+          <t>LF002400KBU</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1766,11 +1766,7 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>567797-LF0</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1785,7 +1781,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LF002400KC1</t>
+          <t>LF002400KBW</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -1793,7 +1789,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1801,11 +1797,7 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>567798-LF0</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1820,7 +1812,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LF002400KC2</t>
+          <t>LF002400KBX</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -1828,7 +1820,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1841,142 +1833,162 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF002400KBY</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>47217</v>
+        <v>46234</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>JERA2026 FIM</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>FIRF GERAES 30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BRBMEBLFI8V4</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LF002400KC0</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>47217</v>
+        <v>46234</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>JERA2026 FIM</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>BMG SEG</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>BRBMEBLFI8V4</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LFSC19002HS</t>
+          <t>LF002400KC0</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>47217</v>
+        <v>46234</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JERA2026 FIM</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>BRBMEBLFI8V4</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>567797-LF0</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
+          <t>LF002400KC1</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>45582</v>
+        <v>46234</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>BRBMEBLFI8V4</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>567798-LF0</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
+          <t>LF002400KC2</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>45582</v>
+        <v>46234</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
+          <t>BRBMEBLFI8V4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -1984,125 +1996,109 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
+          <t>LF00260094N</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45582</v>
+        <v>46839</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>BRABCBLFN7I2</t>
-        </is>
-      </c>
+          <t>FIRF GERAES</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
+          <t>LF002600MAZ</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>45454</v>
+        <v>46965</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI013</t>
-        </is>
-      </c>
+          <t>FIRF GERAES 30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LF002600MB0</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>45454</v>
+        <v>46965</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI021</t>
-        </is>
-      </c>
+          <t>FIRF GERAES</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LF002600MB1</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>45454</v>
+        <v>46965</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI021</t>
-        </is>
-      </c>
+          <t>HORIZONTE FIM</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2113,27 +2109,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>45454</v>
+        <v>47217</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI021</t>
-        </is>
-      </c>
+          <t>JERA2026 FIM</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2144,27 +2136,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC19002CE</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45454</v>
+        <v>47217</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI021</t>
-        </is>
-      </c>
+          <t>JERA2026 FIM</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2175,27 +2163,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC19002HS</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>45455</v>
+        <v>47217</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI039</t>
-        </is>
-      </c>
+          <t>JERA2026 FIM</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2206,25 +2190,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>45455</v>
+        <v>45582</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -2237,16 +2221,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>45455</v>
+        <v>45582</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2255,7 +2239,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2268,16 +2252,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>45461</v>
+        <v>45582</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2286,7 +2270,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -2304,11 +2288,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>45461</v>
+        <v>45454</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2317,7 +2301,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2335,20 +2319,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>45462</v>
+        <v>45454</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -2366,20 +2350,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>45464</v>
+        <v>45454</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -2397,20 +2381,20 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>45464</v>
+        <v>45454</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -2423,25 +2407,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>45582</v>
+        <v>45454</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -2449,30 +2433,30 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>46181</v>
+        <v>45455</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -2480,30 +2464,30 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>46240</v>
+        <v>45455</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2511,30 +2495,30 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>46181</v>
+        <v>45455</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -2542,30 +2526,30 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>46240</v>
+        <v>45461</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2573,30 +2557,30 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>46237</v>
+        <v>45461</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2604,65 +2588,61 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>46237</v>
+        <v>45462</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+          <t>BRBNBRLFI0F8</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>46237</v>
+        <v>45464</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2670,30 +2650,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>46251</v>
+        <v>45464</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -2701,30 +2681,30 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSC19007G2</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>46251</v>
+        <v>45582</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRABCBLFIM30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -2742,27 +2722,23 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>46251</v>
+        <v>46181</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2772,25 +2748,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>45929</v>
+        <v>46240</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -2808,20 +2784,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>46332</v>
+        <v>46181</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -2839,20 +2815,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>46395</v>
+        <v>46240</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -2865,16 +2841,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>46486</v>
+        <v>46237</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2883,7 +2859,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBBDCLTR2X9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -2896,28 +2872,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>46486</v>
+        <v>46237</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2927,32 +2907,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>46486</v>
+        <v>46237</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBBDCLTROH4</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2962,25 +2938,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>46486</v>
+        <v>46251</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLNN8B3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -2993,25 +2969,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>46486</v>
+        <v>46251</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLNN8B3</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -3024,28 +3000,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>46904</v>
+        <v>46251</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3055,25 +3035,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>46904</v>
+        <v>45929</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3086,25 +3066,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>46904</v>
+        <v>46332</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -3117,32 +3097,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>46904</v>
+        <v>46395</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNBB5</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3157,20 +3133,20 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -3183,25 +3159,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>46195</v>
+        <v>46486</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -3214,28 +3190,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>46195</v>
+        <v>46486</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>BRBPACLFIVQ4</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3245,25 +3225,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>46195</v>
+        <v>46486</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -3276,25 +3256,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>46195</v>
+        <v>46486</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -3307,25 +3287,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -3338,25 +3318,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>46199</v>
+        <v>46904</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -3369,25 +3349,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>46199</v>
+        <v>46904</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -3400,28 +3380,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>46199</v>
+        <v>46904</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
+          <t>BRBPACLFIWC2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3431,25 +3415,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>47343</v>
+        <v>46904</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -3457,182 +3441,162 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>46454</v>
+        <v>46195</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>46454</v>
+        <v>46195</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>46454</v>
+        <v>46195</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>46083</v>
+        <v>46195</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>46083</v>
+        <v>46195</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3642,32 +3606,28 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>47217</v>
+        <v>46199</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>609712-LFS</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3677,58 +3637,547 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>47217</v>
+        <v>46199</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>609711-LFS</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>LFSN19009YU</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>FIRF GERAES</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BANCO SAFRA S.A.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>LFSN1900CR5</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>47343</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>FIRF GERAES 30</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>LFSN2200B4M</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>48500</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>FIRF GERAES 30</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3X5</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>LFSN2200B4M</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>48500</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>FIRF GERAES</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3X5</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>LFSN2200B4M</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>48500</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>HORIZONTE FIM</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3X5</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>LFSN2200GD7</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>48570</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>FIRF GERAES 30</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3Y3</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>LFSN2200GD7</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>48570</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>FIRF GERAES</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3Y3</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>LFSN2200GD7</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>48570</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>HORIZONTE FIM</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3Y3</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>Títulos Privados</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>AGIBANK</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CDB3251WXH0</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>46454</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>BMG SEG</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>BRAGBKC00M66</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>AGIBANK</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CDB3251WXH0</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>46454</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>BRAGBKC00M66</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>AGIBANK</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CDB3251WXH0</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>46454</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>REAL FIM</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>BRAGBKC00M66</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BANCO XP</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>LF00240072E</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>BMG SEG</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>BRBCXPLFIKS5</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BANCO XP</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>LF00240072E</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>BRBCXPLFIKS5</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
         <is>
           <t>BANCO BMG S.A.</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>LFSC19002CD</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>609712-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
         <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n">
+      <c r="D119" s="2" t="n">
         <v>47217</v>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>JERA2026</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>

--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -2017,7 +2017,11 @@
           <t>FIRF GERAES</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BRBMEBLFIF17</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2044,7 +2048,11 @@
           <t>FIRF GERAES 30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BRBMEBLFIFX4</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2071,7 +2079,11 @@
           <t>FIRF GERAES</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BRBMEBLFIFX4</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2098,7 +2110,11 @@
           <t>HORIZONTE FIM</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BRBMEBLFIFX4</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2125,7 +2141,11 @@
           <t>JERA2026 FIM</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2152,7 +2172,11 @@
           <t>JERA2026 FIM</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2179,7 +2203,11 @@
           <t>JERA2026 FIM</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7R2</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
